--- a/drafts/42_QA_시트_v1.4.xlsx
+++ b/drafts/42_QA_시트_v1.4.xlsx
@@ -13519,7 +13519,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>9/22</t>
+          <t>9/21</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
